--- a/ig/main/ValueSet-jdv-region-anatomique-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-region-anatomique-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260716085851</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-07-16T08:58:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
